--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU08/HRM/post QA_HRM-2031-0999/Panel 01/front/2031-03-01_10-00-00_ENG_Orion_Stress_Demo_BU08_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU08/HRM/post QA_HRM-2031-0999/Panel 01/front/2031-03-01_10-00-00_ENG_Orion_Stress_Demo_BU08_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.20073</v>
+        <v>16.62544</v>
       </c>
       <c r="D2" t="n">
-        <v>16.36661</v>
+        <v>16.46328</v>
       </c>
       <c r="E2" t="n">
-        <v>16.63394</v>
+        <v>16.47145</v>
       </c>
       <c r="F2" t="n">
-        <v>42.60342</v>
+        <v>41.42758</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05069</v>
+        <v>0.05003</v>
       </c>
       <c r="H2" t="n">
-        <v>1.76643</v>
+        <v>1.81344</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.69746</v>
+        <v>16.87403</v>
       </c>
       <c r="D3" t="n">
-        <v>16.2472</v>
+        <v>16.28321</v>
       </c>
       <c r="E3" t="n">
-        <v>16.45697</v>
+        <v>16.59702</v>
       </c>
       <c r="F3" t="n">
-        <v>41.97091</v>
+        <v>41.7465</v>
       </c>
       <c r="G3" t="n">
-        <v>0.04979</v>
+        <v>0.05062</v>
       </c>
       <c r="H3" t="n">
-        <v>1.77706</v>
+        <v>1.7822</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.61945</v>
+        <v>16.45261</v>
       </c>
       <c r="D4" t="n">
-        <v>16.30607</v>
+        <v>16.12401</v>
       </c>
       <c r="E4" t="n">
-        <v>16.58336</v>
+        <v>16.32688</v>
       </c>
       <c r="F4" t="n">
-        <v>42.68069</v>
+        <v>42.53286</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04982</v>
+        <v>0.04915</v>
       </c>
       <c r="H4" t="n">
-        <v>1.78675</v>
+        <v>1.8114</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.59439</v>
+        <v>16.69208</v>
       </c>
       <c r="D5" t="n">
-        <v>16.55113</v>
+        <v>16.22426</v>
       </c>
       <c r="E5" t="n">
-        <v>16.40059</v>
+        <v>16.5837</v>
       </c>
       <c r="F5" t="n">
-        <v>41.66664</v>
+        <v>41.9688</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04954</v>
+        <v>0.04969</v>
       </c>
       <c r="H5" t="n">
-        <v>1.82409</v>
+        <v>1.8037</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.47194</v>
+        <v>16.60566</v>
       </c>
       <c r="D6" t="n">
-        <v>16.3973</v>
+        <v>16.45835</v>
       </c>
       <c r="E6" t="n">
-        <v>16.41912</v>
+        <v>16.55582</v>
       </c>
       <c r="F6" t="n">
-        <v>41.38961</v>
+        <v>42.20224</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05071</v>
+        <v>0.0501</v>
       </c>
       <c r="H6" t="n">
-        <v>1.79451</v>
+        <v>1.83067</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.68741</v>
+        <v>16.78082</v>
       </c>
       <c r="D7" t="n">
-        <v>16.60549</v>
+        <v>16.67274</v>
       </c>
       <c r="E7" t="n">
-        <v>16.5508</v>
+        <v>16.75628</v>
       </c>
       <c r="F7" t="n">
-        <v>42.558</v>
+        <v>42.7562</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04992</v>
+        <v>0.05008</v>
       </c>
       <c r="H7" t="n">
-        <v>1.79926</v>
+        <v>1.8073</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.75832</v>
+        <v>16.71072</v>
       </c>
       <c r="D8" t="n">
-        <v>16.38066</v>
+        <v>16.37897</v>
       </c>
       <c r="E8" t="n">
-        <v>16.44043</v>
+        <v>16.49626</v>
       </c>
       <c r="F8" t="n">
-        <v>42.82392</v>
+        <v>42.72394</v>
       </c>
       <c r="G8" t="n">
-        <v>0.04913</v>
+        <v>0.05027</v>
       </c>
       <c r="H8" t="n">
-        <v>1.81626</v>
+        <v>1.79015</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.27175</v>
+        <v>16.53005</v>
       </c>
       <c r="D9" t="n">
-        <v>16.24273</v>
+        <v>16.4141</v>
       </c>
       <c r="E9" t="n">
-        <v>16.29977</v>
+        <v>16.51915</v>
       </c>
       <c r="F9" t="n">
-        <v>42.88045</v>
+        <v>41.5447</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05089</v>
+        <v>0.05062</v>
       </c>
       <c r="H9" t="n">
-        <v>1.77686</v>
+        <v>1.79417</v>
       </c>
     </row>
     <row r="10">
@@ -660,22 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.34188</v>
+        <v>16.68886</v>
       </c>
       <c r="D10" t="n">
-        <v>15.99624</v>
+        <v>16.01682</v>
       </c>
       <c r="E10" t="n">
-        <v>16.53879</v>
+        <v>16.66334</v>
       </c>
       <c r="F10" t="n">
-        <v>41.84299</v>
+        <v>41.74345</v>
       </c>
       <c r="G10" t="n">
-        <v>0.04975</v>
+        <v>0.05031</v>
       </c>
       <c r="H10" t="n">
-        <v>1.81473</v>
+        <v>1.79981</v>
       </c>
     </row>
     <row r="11">
@@ -702,10 +702,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.59678</v>
+        <v>0.6065</v>
       </c>
       <c r="D12" t="n">
-        <v>1.1191</v>
+        <v>1.09863</v>
       </c>
     </row>
     <row r="13">
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.5979</v>
+        <v>0.6106</v>
       </c>
       <c r="D13" t="n">
-        <v>1.11835</v>
+        <v>1.08855</v>
       </c>
     </row>
     <row r="14">
@@ -728,10 +728,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.59102</v>
+        <v>0.59789</v>
       </c>
       <c r="D14" t="n">
-        <v>1.10979</v>
+        <v>1.13209</v>
       </c>
     </row>
     <row r="15">
@@ -741,10 +741,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.60812</v>
+        <v>0.60695</v>
       </c>
       <c r="D15" t="n">
-        <v>1.10882</v>
+        <v>1.11218</v>
       </c>
     </row>
     <row r="16">
@@ -754,10 +754,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.60385</v>
+        <v>0.59901</v>
       </c>
       <c r="D16" t="n">
-        <v>1.09103</v>
+        <v>1.08857</v>
       </c>
     </row>
     <row r="17">
@@ -767,10 +767,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.59492</v>
+        <v>0.60188</v>
       </c>
       <c r="D17" t="n">
-        <v>1.10309</v>
+        <v>1.09957</v>
       </c>
     </row>
     <row r="18">
@@ -780,10 +780,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.60146</v>
+        <v>0.6085</v>
       </c>
       <c r="D18" t="n">
-        <v>1.10532</v>
+        <v>1.11042</v>
       </c>
     </row>
     <row r="19">
@@ -793,10 +793,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.6016</v>
+        <v>0.61166</v>
       </c>
       <c r="D19" t="n">
-        <v>1.11653</v>
+        <v>1.10047</v>
       </c>
     </row>
     <row r="20">
@@ -806,10 +806,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.60434</v>
+        <v>0.6064000000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>1.09052</v>
+        <v>1.09416</v>
       </c>
     </row>
   </sheetData>
